--- a/artfynd/A 35032-2026 artfynd.xlsx
+++ b/artfynd/A 35032-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136365561</v>
       </c>
       <c r="B2" t="n">
-        <v>96899</v>
+        <v>96912</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136365580</v>
       </c>
       <c r="B3" t="n">
-        <v>96899</v>
+        <v>96912</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>136365588</v>
       </c>
       <c r="B4" t="n">
-        <v>96899</v>
+        <v>96912</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>136366060</v>
       </c>
       <c r="B5" t="n">
-        <v>96734</v>
+        <v>96747</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>136365574</v>
       </c>
       <c r="B6" t="n">
-        <v>57985</v>
+        <v>57990</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1221,7 +1221,7 @@
         <v>136365595</v>
       </c>
       <c r="B7" t="n">
-        <v>57985</v>
+        <v>57990</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>136356261</v>
       </c>
       <c r="B8" t="n">
-        <v>58144</v>
+        <v>58149</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
         <v>136365637</v>
       </c>
       <c r="B9" t="n">
-        <v>101524</v>
+        <v>101537</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>136365677</v>
       </c>
       <c r="B10" t="n">
-        <v>101524</v>
+        <v>101537</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 35032-2026 artfynd.xlsx
+++ b/artfynd/A 35032-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ10"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1449,49 +1449,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>136365637</v>
+        <v>136357152</v>
       </c>
       <c r="B9" t="n">
-        <v>101537</v>
+        <v>110307</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>220299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Skogsbrink, Ög</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>571671</v>
+        <v>571695</v>
       </c>
       <c r="R9" t="n">
-        <v>6479025</v>
+        <v>6479017</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1532,34 +1528,33 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Emil Lindgren</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Emil Lindgren</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136365637</t>
+          <t>https://artportalen.se/Sighting/136357152</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>136365677</v>
+        <v>136356982</v>
       </c>
       <c r="B10" t="n">
-        <v>101537</v>
+        <v>98189</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1567,38 +1562,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Skogsbrink, Ög</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>571590</v>
+        <v>571728</v>
       </c>
       <c r="R10" t="n">
-        <v>6479049</v>
+        <v>6479018</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1639,23 +1630,236 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Emil Lindgren</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Emil Lindgren</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136356982</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>136365637</v>
+      </c>
+      <c r="B11" t="n">
+        <v>101537</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Skogsbrink, Ög</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>571671</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6479025</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Söderköping</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Drothem</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Emil Lindgren</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Emil Lindgren</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136365637</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>136365677</v>
+      </c>
+      <c r="B12" t="n">
+        <v>101537</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Skogsbrink, Ög</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>571590</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6479049</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Söderköping</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Drothem</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Emil Lindgren</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Emil Lindgren</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136365677</t>
         </is>
@@ -1672,6 +1876,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 35032-2026 artfynd.xlsx
+++ b/artfynd/A 35032-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ12"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
         <v>136365561</v>
       </c>
       <c r="B2" t="n">
-        <v>96912</v>
+        <v>96913</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136365580</v>
       </c>
       <c r="B3" t="n">
-        <v>96912</v>
+        <v>96913</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>136365588</v>
       </c>
       <c r="B4" t="n">
-        <v>96912</v>
+        <v>96913</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>136366060</v>
+        <v>136365574</v>
       </c>
       <c r="B5" t="n">
-        <v>96747</v>
+        <v>57990</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1012,27 +1012,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2682</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kärrkammossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Helodium blandowii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(F.Weber &amp; D.Mohr) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1040,10 +1044,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>571638</v>
+        <v>571766</v>
       </c>
       <c r="R5" t="n">
-        <v>6479041</v>
+        <v>6478752</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1082,9 +1086,8 @@
         <v>0</v>
       </c>
       <c r="AE5" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF5" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1102,13 +1105,13 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136366060</t>
+          <t>https://artportalen.se/Sighting/136365574</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>136365574</v>
+        <v>136365595</v>
       </c>
       <c r="B6" t="n">
         <v>57990</v>
@@ -1151,10 +1154,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>571766</v>
+        <v>571719</v>
       </c>
       <c r="R6" t="n">
-        <v>6478752</v>
+        <v>6478878</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1212,16 +1215,16 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136365574</t>
+          <t>https://artportalen.se/Sighting/136365595</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>136365595</v>
+        <v>136356261</v>
       </c>
       <c r="B7" t="n">
-        <v>57990</v>
+        <v>58149</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1229,16 +1232,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>103023</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1246,25 +1249,26 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Skogsbrink, Ög</t>
+          <t>Skogsbrink, Skogsbrink, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>571719</v>
+        <v>571830</v>
       </c>
       <c r="R7" t="n">
-        <v>6478878</v>
+        <v>6478869</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1294,9 +1298,19 @@
           <t>2026-09-05</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1311,71 +1325,62 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Emil Lindgren</t>
+          <t>Johan Holmgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Emil Lindgren</t>
+          <t>Johan Holmgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136365595</t>
+          <t>https://artportalen.se/Sighting/136356261</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>136356261</v>
+        <v>136357152</v>
       </c>
       <c r="B8" t="n">
-        <v>58149</v>
+        <v>110308</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103023</v>
+        <v>220299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Skogsbrink, Skogsbrink, Ög</t>
+          <t>Skogsbrink, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>571830</v>
+        <v>571695</v>
       </c>
       <c r="R8" t="n">
-        <v>6478869</v>
+        <v>6479017</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1405,19 +1410,9 @@
           <t>2026-09-05</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>12:05</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>12:05</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1432,44 +1427,44 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Johan Holmgren</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Johan Holmgren</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136356261</t>
+          <t>https://artportalen.se/Sighting/136357152</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>136357152</v>
+        <v>136356982</v>
       </c>
       <c r="B9" t="n">
-        <v>110307</v>
+        <v>98190</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220299</v>
+        <v>221945</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1484,10 +1479,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>571695</v>
+        <v>571728</v>
       </c>
       <c r="R9" t="n">
-        <v>6479017</v>
+        <v>6479018</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1545,16 +1540,16 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136357152</t>
+          <t>https://artportalen.se/Sighting/136356982</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>136356982</v>
+        <v>136365637</v>
       </c>
       <c r="B10" t="n">
-        <v>98189</v>
+        <v>101538</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1562,34 +1557,38 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Skogsbrink, Ög</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>571728</v>
+        <v>571671</v>
       </c>
       <c r="R10" t="n">
-        <v>6479018</v>
+        <v>6479025</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1630,33 +1629,34 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136356982</t>
+          <t>https://artportalen.se/Sighting/136365637</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>136365637</v>
+        <v>136365677</v>
       </c>
       <c r="B11" t="n">
-        <v>101537</v>
+        <v>101538</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1692,10 +1692,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>571671</v>
+        <v>571590</v>
       </c>
       <c r="R11" t="n">
-        <v>6479025</v>
+        <v>6479049</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1753,113 +1753,6 @@
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/136365637</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>136365677</v>
-      </c>
-      <c r="B12" t="n">
-        <v>101537</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>Skogsbrink, Ög</t>
-        </is>
-      </c>
-      <c r="Q12" t="n">
-        <v>571590</v>
-      </c>
-      <c r="R12" t="n">
-        <v>6479049</v>
-      </c>
-      <c r="S12" t="n">
-        <v>10</v>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>Östergötland</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>Söderköping</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>Östergötland</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>Drothem</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="AD12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF12" t="inlineStr"/>
-      <c r="AG12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT12" t="inlineStr"/>
-      <c r="AW12" t="inlineStr">
-        <is>
-          <t>Emil Lindgren</t>
-        </is>
-      </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>Emil Lindgren</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
-      <c r="AZ12" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136365677</t>
         </is>
@@ -1877,7 +1770,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 35032-2026 artfynd.xlsx
+++ b/artfynd/A 35032-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136365561</v>
       </c>
       <c r="B2" t="n">
-        <v>96913</v>
+        <v>96926</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136365580</v>
       </c>
       <c r="B3" t="n">
-        <v>96913</v>
+        <v>96926</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>136365588</v>
       </c>
       <c r="B4" t="n">
-        <v>96913</v>
+        <v>96926</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>136365574</v>
       </c>
       <c r="B5" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1114,7 +1114,7 @@
         <v>136365595</v>
       </c>
       <c r="B6" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
         <v>136356261</v>
       </c>
       <c r="B7" t="n">
-        <v>58149</v>
+        <v>58162</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         <v>136357152</v>
       </c>
       <c r="B8" t="n">
-        <v>110308</v>
+        <v>110321</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1447,7 +1447,7 @@
         <v>136356982</v>
       </c>
       <c r="B9" t="n">
-        <v>98190</v>
+        <v>98203</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
         <v>136365637</v>
       </c>
       <c r="B10" t="n">
-        <v>101538</v>
+        <v>101551</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>136365677</v>
       </c>
       <c r="B11" t="n">
-        <v>101538</v>
+        <v>101551</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 35032-2026 artfynd.xlsx
+++ b/artfynd/A 35032-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136365561</v>
       </c>
       <c r="B2" t="n">
-        <v>96926</v>
+        <v>96927</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136365580</v>
       </c>
       <c r="B3" t="n">
-        <v>96926</v>
+        <v>96927</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>136365588</v>
       </c>
       <c r="B4" t="n">
-        <v>96926</v>
+        <v>96927</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         <v>136357152</v>
       </c>
       <c r="B8" t="n">
-        <v>110321</v>
+        <v>110322</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1447,7 +1447,7 @@
         <v>136356982</v>
       </c>
       <c r="B9" t="n">
-        <v>98203</v>
+        <v>98204</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
         <v>136365637</v>
       </c>
       <c r="B10" t="n">
-        <v>101551</v>
+        <v>101552</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>136365677</v>
       </c>
       <c r="B11" t="n">
-        <v>101551</v>
+        <v>101552</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
